--- a/初二五班登分表.xlsx
+++ b/初二五班登分表.xlsx
@@ -17,11 +17,40 @@
 </file>
 
 <file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="ID_349BF3F81AEB4DF2A30311A1867CD45F" descr=" "/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="11613301" cy="3513188"/>
+        </a:xfrm>
+        <a:noFill/>
+        <a:ln w="9525" cap="flat" cmpd="sng">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+</etc:cellImages>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="169" count="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="167" count="167">
   <si>
     <t>测试1</t>
   </si>
@@ -536,15 +565,7 @@
     <t xml:space="preserve">班级：初二五班   科目：                       用途：                       持表人：                    </t>
   </si>
   <si>
-    <t>文档来自初二五班智慧应用平台</t>
-  </si>
-  <si>
-    <t>文档来自初二五班智慧应用平台
-https://luckynum.top/1205</t>
-  </si>
-  <si>
-    <t>表格来自初二五班智慧应用平台
-https://luckynum.top/1205</t>
+    <t>班级：初二五班   科目：______</t>
   </si>
 </sst>
 </file>
@@ -594,7 +615,7 @@
     </font>
     <font>
       <name val="宋体"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
@@ -730,17 +751,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -749,52 +770,6 @@
   <dxfs count="0"/>
   <tableStyles defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16" count="0"/>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>279848</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>11434</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>22193</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name=" " descr=" "/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="11613301" cy="3513188"/>
-        </a:xfrm>
-        <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:effectLst/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1089,11 +1064,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:R133"/>
+  <dimension ref="A1:U133"/>
   <sheetFormatPr defaultRowHeight="14.0" defaultColWidth="10"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="3.75" style="1"/>
-    <col min="2" max="2" customWidth="1" width="5.5625" style="2"/>
+    <col min="1" max="1" customWidth="1" width="3.3515625" style="1"/>
+    <col min="2" max="2" customWidth="1" width="6.1640625" style="2"/>
     <col min="3" max="3" customWidth="1" width="6.2851562" style="3"/>
     <col min="4" max="4" customWidth="1" width="6.2851562" style="4"/>
     <col min="5" max="5" customWidth="1" width="6.2851562" style="3"/>
@@ -1112,9 +1087,9 @@
     <col min="18" max="18" customWidth="1" width="9.996094" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="8:8" ht="15.8">
+    <row r="1" spans="8:8" ht="14.0">
       <c r="A1" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="8"/>
@@ -2235,20 +2210,21 @@
       <c r="Q49" s="5"/>
     </row>
     <row r="50" spans="8:8" ht="46.1" customHeight="1">
-      <c r="A50" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="B50" s="23"/>
-      <c r="C50" s="24"/>
-      <c r="D50" s="24"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="24"/>
-      <c r="G50" s="24"/>
-      <c r="H50" s="24"/>
-      <c r="I50" s="24"/>
-      <c r="J50" s="24"/>
-      <c r="K50" s="24"/>
-      <c r="L50" s="24"/>
+      <c r="A50" s="6" t="str">
+        <f>_xlfn.DISPIMG("ID_349BF3F81AEB4DF2A30311A1867CD45F",1)</f>
+        <v>=DISPIMG("ID_349BF3F81AEB4DF2A30311A1867CD45F",1)</v>
+      </c>
+      <c r="B50" s="22"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="23"/>
+      <c r="I50" s="23"/>
+      <c r="J50" s="23"/>
+      <c r="K50" s="23"/>
+      <c r="L50" s="23"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="13"/>
@@ -2256,7 +2232,7 @@
       <c r="Q50" s="5"/>
     </row>
     <row r="51" spans="8:8" ht="14.0" customHeight="1">
-      <c r="A51" s="25"/>
+      <c r="A51" s="24"/>
       <c r="B51" s="7"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
@@ -3206,7 +3182,7 @@
     </row>
     <row r="124" spans="8:8" ht="14.0" customHeight="1">
       <c r="A124" s="6"/>
-      <c r="B124" s="7"/>
+      <c r="B124" s="25"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -3387,6 +3363,5 @@
     <mergeCell ref="A50:L50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>